--- a/data/samples/vega_payments_integration.xlsx
+++ b/data/samples/vega_payments_integration.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,21 @@
           <t>Actual Finish date</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Effort (hours)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Effort completed (hours)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Effort remaining (hours)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,12 +554,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -589,6 +604,15 @@
         <is>
           <t>2025-11-20</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>22</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +628,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -622,7 +646,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -642,7 +666,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -654,6 +678,15 @@
         <is>
           <t>2025-11-26</t>
         </is>
+      </c>
+      <c r="T3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" t="n">
+        <v>80</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -684,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -717,7 +750,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -729,6 +762,15 @@
         <is>
           <t>2025-12-02</t>
         </is>
+      </c>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="n">
+        <v>24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -754,12 +796,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -805,6 +847,15 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="T5" t="n">
+        <v>80</v>
+      </c>
+      <c r="U5" t="n">
+        <v>80</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="F6" t="inlineStr">
@@ -824,7 +875,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -837,7 +888,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -847,7 +898,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -857,7 +908,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -869,6 +920,15 @@
         <is>
           <t>2025-12-15</t>
         </is>
+      </c>
+      <c r="T6" t="n">
+        <v>32</v>
+      </c>
+      <c r="U6" t="n">
+        <v>32</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -920,7 +980,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -952,6 +1012,15 @@
         <is>
           <t>2025-12-22</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>80</v>
+      </c>
+      <c r="U7" t="n">
+        <v>80</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -982,7 +1051,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -995,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1015,7 +1084,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1027,6 +1096,15 @@
         <is>
           <t>2025-12-28</t>
         </is>
+      </c>
+      <c r="T8" t="n">
+        <v>32</v>
+      </c>
+      <c r="U8" t="n">
+        <v>32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1052,12 +1130,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1103,6 +1181,15 @@
           <t>2026-01-03</t>
         </is>
       </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="F10" t="inlineStr">
@@ -1117,12 +1204,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1155,7 +1242,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1168,8 +1255,25 @@
           <t>2026-01-10</t>
         </is>
       </c>
+      <c r="T10" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" t="n">
+        <v>60</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Approved Budget</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>185000</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1230,8 +1334,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1255,12 +1368,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1283,7 +1396,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1305,6 +1418,15 @@
         <is>
           <t>2026-01-23</t>
         </is>
+      </c>
+      <c r="T12" t="n">
+        <v>60</v>
+      </c>
+      <c r="U12" t="n">
+        <v>60</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1325,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1358,7 +1480,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1368,8 +1490,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>32</v>
+      </c>
+      <c r="U13" t="n">
+        <v>32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1390,7 +1521,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1413,7 +1544,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1423,7 +1554,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1435,6 +1566,15 @@
         <is>
           <t>2026-02-04</t>
         </is>
+      </c>
+      <c r="T14" t="n">
+        <v>80</v>
+      </c>
+      <c r="U14" t="n">
+        <v>80</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1455,7 +1595,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1488,7 +1628,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1500,6 +1640,15 @@
         <is>
           <t>2026-02-12</t>
         </is>
+      </c>
+      <c r="T15" t="n">
+        <v>16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1515,7 +1664,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1553,7 +1702,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1565,6 +1714,15 @@
         <is>
           <t>2026-02-17</t>
         </is>
+      </c>
+      <c r="T16" t="n">
+        <v>44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1580,12 +1738,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1598,7 +1756,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1618,7 +1776,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1628,8 +1786,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
-        </is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>16</v>
+      </c>
+      <c r="U17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1663,7 +1830,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1683,7 +1850,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1695,6 +1862,15 @@
         <is>
           <t>2026-03-02</t>
         </is>
+      </c>
+      <c r="T18" t="n">
+        <v>80</v>
+      </c>
+      <c r="U18" t="n">
+        <v>80</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1718,12 +1894,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1756,7 +1932,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1766,8 +1942,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>60</v>
+      </c>
+      <c r="U19" t="n">
+        <v>60</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1821,7 +2006,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1833,6 +2018,15 @@
         <is>
           <t>2026-03-15</t>
         </is>
+      </c>
+      <c r="T20" t="n">
+        <v>16</v>
+      </c>
+      <c r="U20" t="n">
+        <v>16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1853,7 +2047,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1866,7 +2060,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1886,7 +2080,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1898,6 +2092,15 @@
         <is>
           <t>2026-03-22</t>
         </is>
+      </c>
+      <c r="T21" t="n">
+        <v>40</v>
+      </c>
+      <c r="U21" t="n">
+        <v>40</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1918,7 +2121,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1951,7 +2154,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1961,8 +2164,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>60</v>
+      </c>
+      <c r="U22" t="n">
+        <v>60</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1978,12 +2190,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2026,8 +2238,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>60</v>
+      </c>
+      <c r="U23" t="n">
+        <v>60</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2051,12 +2272,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2099,8 +2320,17 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>40</v>
+      </c>
+      <c r="U24" t="n">
+        <v>40</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2121,7 +2351,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2134,7 +2364,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2144,7 +2374,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2154,7 +2384,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2164,8 +2394,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>32</v>
+      </c>
+      <c r="U25" t="n">
+        <v>32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2181,12 +2420,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2209,7 +2448,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2231,6 +2470,15 @@
         <is>
           <t>2026-04-23</t>
         </is>
+      </c>
+      <c r="T26" t="n">
+        <v>16</v>
+      </c>
+      <c r="U26" t="n">
+        <v>16</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2251,7 +2499,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2294,8 +2542,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>24</v>
+      </c>
+      <c r="U27" t="n">
+        <v>24</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2316,7 +2573,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2329,7 +2586,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2349,7 +2606,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2359,8 +2616,17 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>40</v>
+      </c>
+      <c r="U28" t="n">
+        <v>40</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2381,7 +2647,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2424,8 +2690,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>56</v>
+      </c>
+      <c r="U29" t="n">
+        <v>56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2441,12 +2716,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2489,8 +2764,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>44</v>
+      </c>
+      <c r="U30" t="n">
+        <v>44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2514,12 +2798,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2532,7 +2816,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2542,7 +2826,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2552,7 +2836,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2564,6 +2848,15 @@
         <is>
           <t>2026-05-24</t>
         </is>
+      </c>
+      <c r="T31" t="n">
+        <v>80</v>
+      </c>
+      <c r="U31" t="n">
+        <v>80</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2584,7 +2877,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2627,8 +2920,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>32</v>
+      </c>
+      <c r="U32" t="n">
+        <v>32</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2644,12 +2946,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2658,7 +2960,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2682,13 +2984,22 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
+      </c>
+      <c r="T33" t="n">
+        <v>33</v>
+      </c>
+      <c r="U33" t="n">
+        <v>10</v>
+      </c>
+      <c r="V33" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -2732,7 +3043,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2744,6 +3055,15 @@
         <is>
           <t>2026-06-10</t>
         </is>
+      </c>
+      <c r="T34" t="n">
+        <v>112</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="35">
@@ -2799,6 +3119,15 @@
         <is>
           <t>2026-06-16</t>
         </is>
+      </c>
+      <c r="T35" t="n">
+        <v>33</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -2827,7 +3156,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2862,6 +3191,15 @@
         <is>
           <t>2026-06-22</t>
         </is>
+      </c>
+      <c r="T36" t="n">
+        <v>33</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -2877,12 +3215,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2917,6 +3255,15 @@
         <is>
           <t>2026-06-29</t>
         </is>
+      </c>
+      <c r="T37" t="n">
+        <v>80</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -2932,12 +3279,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>V. Rao</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2950,7 +3297,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2972,6 +3319,15 @@
         <is>
           <t>2026-07-05</t>
         </is>
+      </c>
+      <c r="T38" t="n">
+        <v>24</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -2992,7 +3348,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3005,7 +3361,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3027,6 +3383,15 @@
         <is>
           <t>2026-07-11</t>
         </is>
+      </c>
+      <c r="T39" t="n">
+        <v>32</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -3042,12 +3407,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3070,7 +3435,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3082,6 +3447,15 @@
         <is>
           <t>2026-07-18</t>
         </is>
+      </c>
+      <c r="T40" t="n">
+        <v>24</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
